--- a/product_selector_out/STM32L0 series.xlsx
+++ b/product_selector_out/STM32L0 series.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -99,6 +104,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -34275,9 +34281,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -34602,9 +34608,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -34929,9 +34935,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -35256,9 +35262,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -35583,9 +35589,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -35910,9 +35916,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -36237,9 +36243,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -36564,9 +36570,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="7" t="inlineStr">
@@ -36891,9 +36897,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -37218,9 +37224,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -37545,9 +37551,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="7" t="inlineStr">
@@ -37872,9 +37878,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX23" s="7" t="inlineStr">
@@ -38199,9 +38205,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -38526,9 +38532,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="7" t="inlineStr">
@@ -38853,9 +38859,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="7" t="inlineStr">
@@ -39180,9 +39186,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="7" t="inlineStr">
@@ -39507,9 +39513,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -39834,9 +39840,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="7" t="inlineStr">
@@ -40161,9 +40167,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="7" t="inlineStr">
@@ -40488,9 +40494,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="7" t="inlineStr">
@@ -40815,9 +40821,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX32" s="7" t="inlineStr">
@@ -41142,9 +41148,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX33" s="7" t="inlineStr">
@@ -41469,9 +41475,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX34" s="7" t="inlineStr">
@@ -41796,9 +41802,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX35" s="7" t="inlineStr">
@@ -42123,9 +42129,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX36" s="7" t="inlineStr">
@@ -42450,9 +42456,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX37" s="7" t="inlineStr">
@@ -42777,9 +42783,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX38" s="7" t="inlineStr">
@@ -43104,9 +43110,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX39" s="7" t="inlineStr">
@@ -43431,9 +43437,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX40" s="7" t="inlineStr">
@@ -43758,9 +43764,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX41" s="7" t="inlineStr">
@@ -44085,9 +44091,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX42" s="7" t="inlineStr">
@@ -44412,9 +44418,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX43" s="7" t="inlineStr">
@@ -44739,9 +44745,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX44" s="7" t="inlineStr">
@@ -45066,9 +45072,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX45" s="7" t="inlineStr">
@@ -45393,9 +45399,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX46" s="7" t="inlineStr">
@@ -45720,9 +45726,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX47" s="7" t="inlineStr">
@@ -46047,9 +46053,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX48" s="7" t="inlineStr">
@@ -46374,9 +46380,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX49" s="7" t="inlineStr">
@@ -46701,9 +46707,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX50" s="7" t="inlineStr">
@@ -47028,9 +47034,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW51" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX51" s="7" t="inlineStr">
@@ -47355,9 +47361,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX52" s="7" t="inlineStr">
@@ -47682,9 +47688,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX53" s="7" t="inlineStr">
@@ -48009,9 +48015,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX54" s="7" t="inlineStr">
@@ -48336,9 +48342,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX55" s="7" t="inlineStr">
@@ -48663,9 +48669,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX56" s="7" t="inlineStr">
@@ -48990,9 +48996,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX57" s="7" t="inlineStr">
@@ -49317,9 +49323,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX58" s="7" t="inlineStr">
@@ -49644,9 +49650,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX59" s="7" t="inlineStr">
@@ -49971,9 +49977,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX60" s="7" t="inlineStr">
@@ -50298,9 +50304,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX61" s="7" t="inlineStr">
@@ -50625,9 +50631,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX62" s="7" t="inlineStr">
@@ -52914,9 +52920,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX69" s="7" t="inlineStr">
@@ -53241,9 +53247,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX70" s="7" t="inlineStr">
@@ -53568,9 +53574,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX71" s="7" t="inlineStr">
@@ -53895,9 +53901,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX72" s="7" t="inlineStr">
@@ -54222,9 +54228,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX73" s="7" t="inlineStr">
@@ -54549,9 +54555,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX74" s="7" t="inlineStr">
@@ -54876,9 +54882,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW75" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX75" s="7" t="inlineStr">
@@ -55203,9 +55209,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX76" s="7" t="inlineStr">
@@ -55530,9 +55536,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW77" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX77" s="7" t="inlineStr">
@@ -55857,9 +55863,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW78" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX78" s="7" t="inlineStr">
@@ -56184,9 +56190,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX79" s="7" t="inlineStr">
@@ -56511,9 +56517,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW80" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW80" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX80" s="7" t="inlineStr">
@@ -56838,9 +56844,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX81" s="7" t="inlineStr">
@@ -57165,9 +57171,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX82" s="7" t="inlineStr">
@@ -57492,9 +57498,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX83" s="7" t="inlineStr">
@@ -57819,9 +57825,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX84" s="7" t="inlineStr">
@@ -58146,9 +58152,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX85" s="7" t="inlineStr">
@@ -58473,9 +58479,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX86" s="7" t="inlineStr">
@@ -58800,9 +58806,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX87" s="7" t="inlineStr">
@@ -59127,9 +59133,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW88" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX88" s="7" t="inlineStr">
@@ -59454,9 +59460,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW89" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX89" s="7" t="inlineStr">
@@ -59781,9 +59787,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW90" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX90" s="7" t="inlineStr">
@@ -60108,9 +60114,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW91" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX91" s="7" t="inlineStr">
@@ -60435,9 +60441,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW92" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX92" s="7" t="inlineStr">
@@ -60762,9 +60768,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW93" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX93" s="7" t="inlineStr">
@@ -61089,9 +61095,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW94" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX94" s="7" t="inlineStr">
@@ -61416,9 +61422,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW95" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX95" s="7" t="inlineStr">
@@ -61743,9 +61749,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW96" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX96" s="7" t="inlineStr">
@@ -62070,9 +62076,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW97" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX97" s="7" t="inlineStr">
@@ -62397,9 +62403,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW98" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW98" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX98" s="7" t="inlineStr">
@@ -62724,9 +62730,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW99" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW99" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX99" s="7" t="inlineStr">
@@ -63051,9 +63057,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW100" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW100" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX100" s="7" t="inlineStr">
@@ -63378,9 +63384,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW101" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW101" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX101" s="7" t="inlineStr">
@@ -63705,9 +63711,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW102" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW102" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX102" s="7" t="inlineStr">
@@ -64032,9 +64038,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW103" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW103" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX103" s="7" t="inlineStr">
@@ -64359,9 +64365,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW104" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW104" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX104" s="7" t="inlineStr">
@@ -64686,9 +64692,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW105" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW105" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX105" s="7" t="inlineStr">
@@ -65013,9 +65019,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW106" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW106" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX106" s="7" t="inlineStr">
@@ -65340,9 +65346,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW107" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW107" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX107" s="7" t="inlineStr">
@@ -65667,9 +65673,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW108" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW108" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX108" s="7" t="inlineStr">
@@ -65994,9 +66000,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW109" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW109" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX109" s="7" t="inlineStr">
@@ -66321,9 +66327,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW110" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW110" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX110" s="7" t="inlineStr">
@@ -66422,7 +66428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -66453,7 +66459,2052 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32L011F4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32L071KB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32L011K3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32L081KZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32L071KZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32L071CZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L011D4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L011K4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L071RZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L041E6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L071VZ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L011G3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L021G4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L031F4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L051T6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32L021F4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L051T8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L011E3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L011F3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L031G4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32L041K6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L031K4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32L071VB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32L041C6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32L081CZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32L041F6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32L011E4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32L021K4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32L031E6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32L011D3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32L031G6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32L021D4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32L031F6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32L031C4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32L031K6</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32L071V8</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32L051K6</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32L031E4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32L041G6</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32L071K8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32L071C8</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32L071CB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32L011G4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32L031C6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32L071RB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32L081CB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32L051C8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32L051R6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32L051K8</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32L051C6</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32L051R8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32L072KZ</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32L072KB</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32L062C8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32L082CZ</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32L072V8</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32L082KZ</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32L072CZ</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32L082KB</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32L072RZ</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32L062K8</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32L072VB</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32L072RB</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32L052T8</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32L072CB</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32L052T6</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32L072VZ</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32L052K8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32L052C8</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32L052C6</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32L052R6</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32L052R8</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32L052K6</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32L073CZ</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32L063C8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32L053R6</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32L073VB</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32L083RB</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32L083VZ</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32L083VB</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32L073RB</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32L073VZ</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32L073RZ</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32L073CB</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32L083CZ</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32L083V8</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32L083CB</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32L083RZ</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32L073V8</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32L053C6</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32L063R8</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32L053C8</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32L053R8</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L0 series.xlsx
+++ b/product_selector_out/STM32L0 series.xlsx
@@ -21588,7 +21588,7 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l082cz.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -54335,9 +54335,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -54555,14 +54555,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY74" s="6" t="inlineStr">
@@ -54635,9 +54635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -66428,7 +66428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67694,7 +67694,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L082KZ</t>
+          <t>STM32L072CZ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -67709,14 +67709,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L072CZ</t>
+          <t>STM32L082KB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -67731,14 +67731,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L082KB</t>
+          <t>STM32L072RZ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -67753,14 +67753,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L072RZ</t>
+          <t>STM32L062K8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -67775,14 +67775,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L062K8</t>
+          <t>STM32L072VB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -67797,14 +67797,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L072VB</t>
+          <t>STM32L072RB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -67826,7 +67826,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L072RB</t>
+          <t>STM32L052T8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -67841,14 +67841,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L052T8</t>
+          <t>STM32L072CB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -67863,14 +67863,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L072CB</t>
+          <t>STM32L052T6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -67885,14 +67885,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L052T6</t>
+          <t>STM32L072VZ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -67907,14 +67907,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L072VZ</t>
+          <t>STM32L052K8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -67929,14 +67929,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L052K8</t>
+          <t>STM32L052C8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -67958,7 +67958,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L052C8</t>
+          <t>STM32L052C6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -67980,7 +67980,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L052C6</t>
+          <t>STM32L052R6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -68002,7 +68002,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L052R6</t>
+          <t>STM32L052R8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -68024,7 +68024,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L052R8</t>
+          <t>STM32L052K6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -68046,7 +68046,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L052K6</t>
+          <t>STM32L073CZ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -68061,14 +68061,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L073CZ</t>
+          <t>STM32L063C8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -68083,14 +68083,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L063C8</t>
+          <t>STM32L053R6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -68112,7 +68112,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L053R6</t>
+          <t>STM32L073VB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -68127,14 +68127,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L073VB</t>
+          <t>STM32L083RB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -68156,7 +68156,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L083RB</t>
+          <t>STM32L083VZ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -68178,7 +68178,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L083VZ</t>
+          <t>STM32L083VB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -68200,7 +68200,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L083VB</t>
+          <t>STM32L073RB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -68222,7 +68222,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L073RB</t>
+          <t>STM32L073VZ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -68244,7 +68244,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L073VZ</t>
+          <t>STM32L073RZ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -68266,7 +68266,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L073RZ</t>
+          <t>STM32L073CB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -68288,7 +68288,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L073CB</t>
+          <t>STM32L083CZ</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -68310,7 +68310,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L083CZ</t>
+          <t>STM32L083V8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -68332,7 +68332,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L083V8</t>
+          <t>STM32L083CB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -68354,7 +68354,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L083CB</t>
+          <t>STM32L083RZ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -68376,7 +68376,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32L083RZ</t>
+          <t>STM32L073V8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -68398,7 +68398,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32L073V8</t>
+          <t>STM32L053C6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -68413,14 +68413,14 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32L053C6</t>
+          <t>STM32L063R8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -68442,7 +68442,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32L063R8</t>
+          <t>STM32L053C8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -68464,7 +68464,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32L053C8</t>
+          <t>STM32L053R8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -68478,28 +68478,6 @@
         </is>
       </c>
       <c r="D93" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32L053R8</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
         <is>
           <t>Table 24. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>

--- a/product_selector_out/STM32L0 series.xlsx
+++ b/product_selector_out/STM32L0 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM110"/>
+  <dimension ref="A1:BN110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.40625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l081cb.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l021d4.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l021d4.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l081cb.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l021d4.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l021d4.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -15702,6 +15929,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l081cb.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l010f4.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l010rb.pdf</t>
         </is>
       </c>
@@ -18645,6 +18917,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l010k8.pdf</t>
         </is>
       </c>
@@ -18972,6 +19249,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l010k8.pdf</t>
         </is>
       </c>
@@ -19299,6 +19581,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l010f4.pdf</t>
         </is>
       </c>
@@ -19626,6 +19913,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l010c6.pdf</t>
         </is>
       </c>
@@ -19953,6 +20245,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -20280,6 +20577,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -20607,6 +20909,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l062c8.pdf</t>
         </is>
       </c>
@@ -20934,6 +21241,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l082cz.pdf</t>
         </is>
       </c>
@@ -21261,6 +21573,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -21591,6 +21908,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -21915,6 +22237,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -22242,6 +22569,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l082cz.pdf</t>
         </is>
       </c>
@@ -22569,6 +22901,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -22896,6 +23233,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l062c8.pdf</t>
         </is>
       </c>
@@ -23223,6 +23565,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -23550,6 +23897,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -23877,6 +24229,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -24204,6 +24561,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -24531,6 +24893,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -24858,6 +25225,11 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -25185,6 +25557,11 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -25512,6 +25889,11 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -25839,6 +26221,11 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -26166,6 +26553,11 @@
       </c>
       <c r="BM88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -26493,6 +26885,11 @@
       </c>
       <c r="BM89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -26820,6 +27217,11 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -27147,6 +27549,11 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l073cb.pdf</t>
         </is>
       </c>
@@ -27474,6 +27881,11 @@
       </c>
       <c r="BM92" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN92" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l063c8.pdf</t>
         </is>
       </c>
@@ -27801,6 +28213,11 @@
       </c>
       <c r="BM93" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l053c6.pdf</t>
         </is>
       </c>
@@ -28128,6 +28545,11 @@
       </c>
       <c r="BM94" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l073cb.pdf</t>
         </is>
       </c>
@@ -28455,6 +28877,11 @@
       </c>
       <c r="BM95" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN95" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l083cb.pdf</t>
         </is>
       </c>
@@ -28782,6 +29209,11 @@
       </c>
       <c r="BM96" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN96" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l083cb.pdf</t>
         </is>
       </c>
@@ -29109,6 +29541,11 @@
       </c>
       <c r="BM97" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN97" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l083cb.pdf</t>
         </is>
       </c>
@@ -29436,6 +29873,11 @@
       </c>
       <c r="BM98" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN98" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l073cb.pdf</t>
         </is>
       </c>
@@ -29763,6 +30205,11 @@
       </c>
       <c r="BM99" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN99" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l073cb.pdf</t>
         </is>
       </c>
@@ -30090,6 +30537,11 @@
       </c>
       <c r="BM100" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN100" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l073cb.pdf</t>
         </is>
       </c>
@@ -30417,6 +30869,11 @@
       </c>
       <c r="BM101" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN101" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l073cb.pdf</t>
         </is>
       </c>
@@ -30744,6 +31201,11 @@
       </c>
       <c r="BM102" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN102" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l083cb.pdf</t>
         </is>
       </c>
@@ -31071,6 +31533,11 @@
       </c>
       <c r="BM103" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN103" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l083cb.pdf</t>
         </is>
       </c>
@@ -31398,6 +31865,11 @@
       </c>
       <c r="BM104" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN104" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l083cb.pdf</t>
         </is>
       </c>
@@ -31725,6 +32197,11 @@
       </c>
       <c r="BM105" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN105" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l083cb.pdf</t>
         </is>
       </c>
@@ -32052,6 +32529,11 @@
       </c>
       <c r="BM106" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN106" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l073cb.pdf</t>
         </is>
       </c>
@@ -32379,6 +32861,11 @@
       </c>
       <c r="BM107" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN107" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l053c6.pdf</t>
         </is>
       </c>
@@ -32706,6 +33193,11 @@
       </c>
       <c r="BM108" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN108" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l063c8.pdf</t>
         </is>
       </c>
@@ -33033,6 +33525,11 @@
       </c>
       <c r="BM109" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN109" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l053c6.pdf</t>
         </is>
       </c>
@@ -33360,12 +33857,17 @@
       </c>
       <c r="BM110" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN110" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l053c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -33386,16 +33888,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -33408,6 +33908,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -33427,7 +33928,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -33543,7 +34046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM110"/>
+  <dimension ref="A1:BN110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33611,6 +34114,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33944,6 +34448,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -34039,6 +34548,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -34361,7 +34871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34688,7 +35203,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35015,7 +35535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35342,7 +35867,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35669,7 +36199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35996,7 +36531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36323,7 +36863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36650,7 +37195,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36977,7 +37527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37304,7 +37859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37631,7 +38191,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37958,7 +38523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38285,7 +38855,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38612,7 +39187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38939,7 +39519,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39266,7 +39851,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39593,7 +40183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39920,7 +40515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40247,7 +40847,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40574,7 +41179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40901,7 +41511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41228,7 +41843,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41555,7 +42175,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41882,7 +42507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42209,7 +42839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42536,7 +43171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42863,7 +43503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43190,7 +43835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43517,7 +44167,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43844,7 +44499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44171,7 +44831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44498,7 +45163,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44825,7 +45495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45152,7 +45827,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45479,7 +46159,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45806,7 +46491,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46133,7 +46823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46460,7 +47155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46787,7 +47487,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47114,7 +47819,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47441,7 +48151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47768,7 +48483,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48095,7 +48815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48422,7 +49147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48749,7 +49479,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49076,7 +49811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49403,7 +50143,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49730,7 +50475,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50057,7 +50807,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50384,7 +51139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50711,7 +51471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51038,7 +51803,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51365,7 +52135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51692,7 +52467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52019,7 +52799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52346,7 +53131,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52673,7 +53463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53000,7 +53795,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53327,7 +54127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53654,7 +54459,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53981,7 +54791,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54308,7 +55123,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54640,6 +55460,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -54962,7 +55787,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55289,7 +56119,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55616,7 +56451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55943,7 +56783,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56270,7 +57115,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56597,7 +57447,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56924,7 +57779,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57251,7 +58111,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57578,7 +58443,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57905,7 +58775,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58232,7 +59107,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58559,7 +59439,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58886,7 +59771,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59213,7 +60103,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM88" s="6" t="inlineStr">
+      <c r="BM88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59540,7 +60435,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM89" s="6" t="inlineStr">
+      <c r="BM89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59867,7 +60767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
+      <c r="BM90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60194,7 +61099,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM91" s="6" t="inlineStr">
+      <c r="BM91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60521,7 +61431,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM92" s="6" t="inlineStr">
+      <c r="BM92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN92" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60848,7 +61763,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM93" s="6" t="inlineStr">
+      <c r="BM93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61175,7 +62095,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM94" s="6" t="inlineStr">
+      <c r="BM94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61502,7 +62427,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM95" s="6" t="inlineStr">
+      <c r="BM95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN95" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61829,7 +62759,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM96" s="6" t="inlineStr">
+      <c r="BM96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN96" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62156,7 +63091,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM97" s="6" t="inlineStr">
+      <c r="BM97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN97" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62483,7 +63423,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM98" s="6" t="inlineStr">
+      <c r="BM98" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN98" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62810,7 +63755,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM99" s="6" t="inlineStr">
+      <c r="BM99" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN99" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63137,7 +64087,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM100" s="6" t="inlineStr">
+      <c r="BM100" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN100" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63464,7 +64419,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM101" s="6" t="inlineStr">
+      <c r="BM101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN101" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63791,7 +64751,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM102" s="6" t="inlineStr">
+      <c r="BM102" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN102" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -64118,7 +65083,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM103" s="6" t="inlineStr">
+      <c r="BM103" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN103" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -64445,7 +65415,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM104" s="6" t="inlineStr">
+      <c r="BM104" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN104" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -64772,7 +65747,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM105" s="6" t="inlineStr">
+      <c r="BM105" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN105" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -65099,7 +66079,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM106" s="6" t="inlineStr">
+      <c r="BM106" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN106" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -65426,7 +66411,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM107" s="6" t="inlineStr">
+      <c r="BM107" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN107" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -65753,7 +66743,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM108" s="6" t="inlineStr">
+      <c r="BM108" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN108" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -66080,7 +67075,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM109" s="6" t="inlineStr">
+      <c r="BM109" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN109" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -66407,7 +67407,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM110" s="6" t="inlineStr">
+      <c r="BM110" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN110" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -66415,8 +67420,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
